--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.40876187811004</v>
+        <v>3.153923805192882</v>
       </c>
       <c r="D2" t="n">
-        <v>35.28137591526824</v>
+        <v>5.733223586231089</v>
       </c>
       <c r="E2" t="n">
-        <v>9.250969905899412</v>
+        <v>1.503282609708654</v>
       </c>
       <c r="F2" t="n">
-        <v>11.52649670162923</v>
+        <v>1.873055714014749</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.18093108651849</v>
+        <v>4.904401301559254</v>
       </c>
       <c r="D3" t="n">
-        <v>36.47318672915906</v>
+        <v>5.926892843488347</v>
       </c>
       <c r="E3" t="n">
-        <v>9.250969905899412</v>
+        <v>1.503282609708654</v>
       </c>
       <c r="F3" t="n">
-        <v>11.52649670162923</v>
+        <v>1.873055714014749</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.561701482139584</v>
+        <v>0.9037764908476824</v>
       </c>
       <c r="D4" t="n">
-        <v>18.91175087049461</v>
+        <v>3.073159516455375</v>
       </c>
       <c r="E4" t="n">
-        <v>9.250969905899412</v>
+        <v>1.503282609708654</v>
       </c>
       <c r="F4" t="n">
-        <v>11.52649670162923</v>
+        <v>1.873055714014749</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.21506170825448</v>
+        <v>2.309947527591353</v>
       </c>
       <c r="D5" t="n">
-        <v>10.95138672705592</v>
+        <v>1.779600343146587</v>
       </c>
       <c r="E5" t="n">
-        <v>9.250969905899412</v>
+        <v>1.503282609708654</v>
       </c>
       <c r="F5" t="n">
-        <v>11.52649670162923</v>
+        <v>1.873055714014749</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.10128131360378</v>
+        <v>4.566458213460614</v>
       </c>
       <c r="D6" t="n">
-        <v>6.698717630229675</v>
+        <v>1.088541614912322</v>
       </c>
       <c r="E6" t="n">
-        <v>9.250969905899412</v>
+        <v>1.503282609708654</v>
       </c>
       <c r="F6" t="n">
-        <v>11.52649670162923</v>
+        <v>1.873055714014749</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.74460036666086</v>
+        <v>2.39599755958239</v>
       </c>
       <c r="D7" t="n">
-        <v>12.45607069442361</v>
+        <v>2.024111487843836</v>
       </c>
       <c r="E7" t="n">
-        <v>9.250969905899412</v>
+        <v>1.503282609708654</v>
       </c>
       <c r="F7" t="n">
-        <v>11.52649670162923</v>
+        <v>1.873055714014749</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.056419875323094</v>
+        <v>0.8216682297400028</v>
       </c>
       <c r="D8" t="n">
-        <v>8.304601283943436</v>
+        <v>1.349497708640808</v>
       </c>
       <c r="E8" t="n">
-        <v>9.250969905899412</v>
+        <v>1.503282609708654</v>
       </c>
       <c r="F8" t="n">
-        <v>11.52649670162923</v>
+        <v>1.873055714014749</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.22537680886665</v>
+        <v>4.42412373144083</v>
       </c>
       <c r="D9" t="n">
-        <v>30.21655638036381</v>
+        <v>4.910190411809119</v>
       </c>
       <c r="E9" t="n">
-        <v>9.250969905899412</v>
+        <v>1.503282609708654</v>
       </c>
       <c r="F9" t="n">
-        <v>11.52649670162923</v>
+        <v>1.873055714014749</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
